--- a/languages/es/output/import/西班牙语专四基础.xlsx
+++ b/languages/es/output/import/西班牙语专四基础.xlsx
@@ -11275,7 +11275,7 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>[ˈnumeɾo] 数量&lt;名&gt;</t>
+          <t>[ˈnumeɾo] 数字；号码&lt;名&gt;</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="D340" s="1" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>数字；号码</t>
         </is>
       </c>
       <c r="E340" s="1" t="inlineStr">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="B488" s="1" t="inlineStr">
         <is>
-          <t>[rekoɾˈdaɾ] 记住&lt;动&gt;</t>
+          <t>[rekoɾˈdaɾ] 记得；提醒&lt;动&gt;</t>
         </is>
       </c>
       <c r="C488" s="1" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="D488" s="1" t="inlineStr">
         <is>
-          <t>记住</t>
+          <t>记得；提醒</t>
         </is>
       </c>
       <c r="E488" s="1" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="B515" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾopjo] 拥有&lt;形&gt;</t>
+          <t>[ˈpɾopjo] 自己的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C515" s="1" t="inlineStr">
@@ -16865,7 +16865,7 @@
       </c>
       <c r="D515" s="1" t="inlineStr">
         <is>
-          <t>拥有</t>
+          <t>自己的</t>
         </is>
       </c>
       <c r="E515" s="1" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="B540" s="1" t="inlineStr">
         <is>
-          <t>[ˈkampo] 领域&lt;名&gt;</t>
+          <t>[ˈkampo] 田野；领域&lt;名&gt;</t>
         </is>
       </c>
       <c r="C540" s="1" t="inlineStr">
@@ -17665,7 +17665,7 @@
       </c>
       <c r="D540" s="1" t="inlineStr">
         <is>
-          <t>领域</t>
+          <t>田野；领域</t>
         </is>
       </c>
       <c r="E540" s="1" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="B607" s="1" t="inlineStr">
         <is>
-          <t>[kaˈreɾa] 职业生涯&lt;名&gt;</t>
+          <t>[kaˈreɾa] 职业；赛跑&lt;名&gt;</t>
         </is>
       </c>
       <c r="C607" s="1" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="D607" s="1" t="inlineStr">
         <is>
-          <t>职业生涯</t>
+          <t>职业；赛跑</t>
         </is>
       </c>
       <c r="E607" s="1" t="inlineStr">
@@ -31531,7 +31531,7 @@
       </c>
       <c r="B974" s="1" t="inlineStr">
         <is>
-          <t>[ˈkopa] 杯子&lt;名&gt;</t>
+          <t>[ˈkopa] 高脚杯；树冠&lt;名&gt;</t>
         </is>
       </c>
       <c r="C974" s="1" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="D974" s="1" t="inlineStr">
         <is>
-          <t>杯子</t>
+          <t>高脚杯；树冠</t>
         </is>
       </c>
       <c r="E974" s="1" t="inlineStr">
@@ -44075,7 +44075,7 @@
       </c>
       <c r="B1367" s="1" t="inlineStr">
         <is>
-          <t>[ˈtomo] 我拿&lt;名&gt;</t>
+          <t>[ˈtomo] 卷；册&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1367" s="1" t="inlineStr">
@@ -44085,7 +44085,7 @@
       </c>
       <c r="D1367" s="1" t="inlineStr">
         <is>
-          <t>我拿</t>
+          <t>卷；册</t>
         </is>
       </c>
       <c r="E1367" s="1" t="inlineStr">
@@ -49951,7 +49951,7 @@
       </c>
       <c r="B1551" s="1" t="inlineStr">
         <is>
-          <t>[sopoɾˈtaɾ] 忍受&lt;动&gt;</t>
+          <t>[sopoɾˈtaɾ] 忍受；承受&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1551" s="1" t="inlineStr">
@@ -49961,7 +49961,7 @@
       </c>
       <c r="D1551" s="1" t="inlineStr">
         <is>
-          <t>忍受</t>
+          <t>忍受；承受</t>
         </is>
       </c>
       <c r="E1551" s="1" t="inlineStr">
@@ -58899,7 +58899,7 @@
       </c>
       <c r="B1831" s="1" t="inlineStr">
         <is>
-          <t>[ˈpasta] 面食&lt;名&gt;</t>
+          <t>[ˈpasta] 面团；意大利面；钱&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1831" s="1" t="inlineStr">
@@ -58909,7 +58909,7 @@
       </c>
       <c r="D1831" s="1" t="inlineStr">
         <is>
-          <t>面食</t>
+          <t>面团；意大利面；钱</t>
         </is>
       </c>
       <c r="E1831" s="1" t="inlineStr">

--- a/languages/es/output/import/西班牙语专四基础.xlsx
+++ b/languages/es/output/import/西班牙语专四基础.xlsx
@@ -23183,7 +23183,7 @@
       </c>
       <c r="B713" s="1" t="inlineStr">
         <is>
-          <t>[inteliˈxente/ [ĩn̪.t̪e.liˈxẽn̪.t̪e]] 聪明的&lt;形&gt;</t>
+          <t>[inteliˈxente] 聪明的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C713" s="1" t="inlineStr">

--- a/languages/es/output/import/西班牙语专四基础.xlsx
+++ b/languages/es/output/import/西班牙语专四基础.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>[ke] （关系代词/连接词）&lt;连&gt;</t>
+          <t>[ke] 关系代词/连接词&lt;连&gt;</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -477,7 +477,7 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>（关系代词/连接词）</t>
+          <t>关系代词/连接词</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>[la] 定冠词（阴性单数）&lt;限定&gt;</t>
+          <t>[la] 定冠词[阴性单数]&lt;限定&gt;</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>定冠词（阴性单数）</t>
+          <t>定冠词[阴性单数]</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>[un] 一个（阳性）&lt;限定&gt;</t>
+          <t>[un] 一个[阳性]&lt;限定&gt;</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>一个（阳性）</t>
+          <t>一个[阳性]</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>[me] 我（宾格）&lt;代&gt;</t>
+          <t>[me] 我[宾格]&lt;代&gt;</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>我（宾格）</t>
+          <t>我[宾格]</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>[una] 一个（阴性）&lt;限定&gt;</t>
+          <t>[una] 一个[阴性]&lt;限定&gt;</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>一个（阴性）</t>
+          <t>一个[阴性]</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>[te] 你（宾格）&lt;代&gt;</t>
+          <t>[te] 你[宾格]&lt;代&gt;</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>你（宾格）</t>
+          <t>你[宾格]</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>[le] 他/她/您（与格）&lt;代&gt;</t>
+          <t>[le] 他/她/您[与格]&lt;代&gt;</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>他/她/您（与格）</t>
+          <t>他/她/您[与格]</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>[esta] 这个（阴性）&lt;限定&gt;</t>
+          <t>[esta] 这个[阴性]&lt;限定&gt;</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>这个（阴性）</t>
+          <t>这个[阴性]</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>[aj] 有（存在）&lt;动&gt;</t>
+          <t>[aj] 有[存在]&lt;动&gt;</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>有（存在）</t>
+          <t>有[存在]</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>先生。&lt;名&gt;</t>
+          <t>[seˈɲoɾ] 先生&lt;名&gt;</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr"/>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t>夫人。&lt;名&gt;</t>
+          <t>[seˈɲoɾa] 夫人&lt;名&gt;</t>
         </is>
       </c>
       <c r="C354" s="1" t="inlineStr"/>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>博士。&lt;名&gt;</t>
+          <t>[doɡˈtoɾ] 博士&lt;名&gt;</t>
         </is>
       </c>
       <c r="C374" s="1" t="inlineStr"/>
@@ -27435,7 +27435,7 @@
       </c>
       <c r="B846" s="1" t="inlineStr">
         <is>
-          <t>[ˈia] ia&lt;名&gt;</t>
+          <t>[ˈia] 人工智能；AI&lt;名&gt;</t>
         </is>
       </c>
       <c r="C846" s="1" t="inlineStr">
@@ -27445,7 +27445,7 @@
       </c>
       <c r="D846" s="1" t="inlineStr">
         <is>
-          <t>ia</t>
+          <t>人工智能</t>
         </is>
       </c>
       <c r="E846" s="1" t="inlineStr">
@@ -36551,7 +36551,7 @@
       </c>
       <c r="B1131" s="1" t="inlineStr">
         <is>
-          <t>博士。&lt;名&gt;</t>
+          <t>[doɡˈtoɾa] 博士&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1131" s="1" t="inlineStr"/>
@@ -60435,13 +60435,13 @@
       </c>
       <c r="B1879" s="1" t="inlineStr">
         <is>
-          <t>s。&lt;名&gt;</t>
+          <t>[seˈɣundo] 秒；秒钟&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1879" s="1" t="inlineStr"/>
       <c r="D1879" s="1" t="inlineStr">
         <is>
-          <t>s。</t>
+          <t>秒</t>
         </is>
       </c>
       <c r="E1879" s="1" t="inlineStr">

--- a/languages/es/output/import/西班牙语专四基础.xlsx
+++ b/languages/es/output/import/西班牙语专四基础.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>/de/</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>ke</t>
+          <t>/ke/</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>/no/</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>la</t>
+          <t>/la/</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>/un/</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>por</t>
+          <t>/por/</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>me</t>
+          <t>/me/</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>una</t>
+          <t>/una/</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>/se/</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>te</t>
+          <t>/te/</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>para</t>
+          <t>/para/</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>mi</t>
+          <t>/mi/</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>pero</t>
+          <t>/pero/</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>[ˈsi] 是的&lt;名&gt;</t>
+          <t>[/ˈsi/] 是的&lt;副&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>是的</t>
+          <t>是的&lt;副&gt;</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>/si/</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>bjen</t>
+          <t>/bjen/</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>eso</t>
+          <t>/eso/</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>su</t>
+          <t>/su/</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>ʒo</t>
+          <t>/ʒo/</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>komo</t>
+          <t>/komo/</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>tu</t>
+          <t>/tu/</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>/le/</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>todo</t>
+          <t>/todo/</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>/ja/</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>[aora] 现在&lt;副&gt;</t>
+          <t>[/aˈoɾa/] 现在&lt;副&gt;</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>aora</t>
+          <t>/aˈoɾa/</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>muj</t>
+          <t>/muj/</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -1555,13 +1555,17 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>哈&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr"/>
+          <t>[[ˈa] （haber的第三人称单数）已经；有&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>/a/</t>
+        </is>
+      </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>哈</t>
+          <t>（haber的第三人称单数）已经；有</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1588,7 +1592,7 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>esta</t>
+          <t>/esta/</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
@@ -1684,7 +1688,7 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>/algo/</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
@@ -1716,7 +1720,7 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>aj</t>
+          <t>/aj/</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
@@ -1844,7 +1848,7 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>kwando</t>
+          <t>/kwando/</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
@@ -1972,7 +1976,7 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>nada</t>
+          <t>/nada/</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
@@ -2036,7 +2040,7 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>este</t>
+          <t>/este/</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
@@ -2095,7 +2099,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>[poˈdeɾ] 电源&lt;名&gt;</t>
+          <t>[/poˈdeɾ/] 能够；权力；能力&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -2105,7 +2109,7 @@
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>电源</t>
+          <t>能够；权力；能力</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -2260,7 +2264,7 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>grasjas</t>
+          <t>/grasjas/</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
@@ -2644,7 +2648,7 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>ola</t>
+          <t>/ola/</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
@@ -2767,7 +2771,7 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>[tan] 所以&lt;副&gt;</t>
+          <t>[/tan/] 如此；那么&lt;adv&gt;</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2777,7 +2781,7 @@
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>所以</t>
+          <t>如此；那么</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -3279,7 +3283,7 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>[ˈaθe] 前&lt;介&gt;</t>
+          <t>[/ˈaθe/] 做；……以前（表时间）&lt;prep&gt;</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -3289,7 +3293,7 @@
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>前</t>
+          <t>做；……以前（表时间）</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
@@ -4338,7 +4342,11 @@
           <t>[seˈɲoɾ] 先生&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr"/>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>/seˈɲoɾ/</t>
+        </is>
+      </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
           <t>先生。</t>
@@ -5547,7 +5555,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>[ɡusˈtaɾ] 喜欢&lt;动&gt;</t>
+          <t>[/ɡusˈtaɾ/] 使喜欢；被喜爱&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -5557,7 +5565,7 @@
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>喜欢</t>
+          <t>使喜欢；被喜爱&lt;动&gt;</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
@@ -5771,7 +5779,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>[deˈbeɾ] 职责&lt;名&gt;</t>
+          <t>[/deˈbeɾ/] 应该，必须&lt;动&gt;；职责&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -5781,7 +5789,7 @@
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>职责</t>
+          <t>应该，必须&lt;动&gt;；职责&lt;名&gt;</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
@@ -5995,7 +6003,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>[impoɾˈtaɾ] 进口&lt;动&gt;</t>
+          <t>[/impoɾˈtaɾ/] 要紧；关系到；进口&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -6005,7 +6013,7 @@
       </c>
       <c r="D175" s="1" t="inlineStr">
         <is>
-          <t>进口</t>
+          <t>要紧；关系到；进口</t>
         </is>
       </c>
       <c r="E175" s="1" t="inlineStr">
@@ -6795,7 +6803,7 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>[usˈtedes] 你&lt;代&gt;</t>
+          <t>[/usˈtedes/] 你们；您们&lt;pron&gt;</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
@@ -6805,7 +6813,7 @@
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>你们；您们</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
@@ -7211,7 +7219,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>[kaˈɾiɲo] 蜂蜜&lt;名&gt;</t>
+          <t>[/kaˈɾiɲo/] 亲爱的；喜爱；关怀&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -7221,7 +7229,7 @@
       </c>
       <c r="D213" s="1" t="inlineStr">
         <is>
-          <t>蜂蜜</t>
+          <t>亲爱的；喜爱；关怀</t>
         </is>
       </c>
       <c r="E213" s="1" t="inlineStr">
@@ -7595,7 +7603,7 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>[suˈpwesto] 课程&lt;名&gt;</t>
+          <t>[/suˈpwesto/] 假定的；当然（por supuesto）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
@@ -7605,7 +7613,7 @@
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>课程</t>
+          <t>假定的；当然（por supuesto）</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
@@ -7659,7 +7667,7 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>[aˈdjos] 再见&lt;名&gt;</t>
+          <t>[/aˈdjos/] 再见&lt;叹&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
@@ -7669,7 +7677,7 @@
       </c>
       <c r="D227" s="1" t="inlineStr">
         <is>
-          <t>再见</t>
+          <t>再见&lt;叹&gt;</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
@@ -8331,7 +8339,7 @@
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t>[pɾiˈmeɾo] 第一&lt;名&gt;</t>
+          <t>[/pɾiˈmeɾo/] 第一的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr">
@@ -8341,7 +8349,7 @@
       </c>
       <c r="D248" s="1" t="inlineStr">
         <is>
-          <t>第一</t>
+          <t>第一的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E248" s="1" t="inlineStr">
@@ -9643,7 +9651,7 @@
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>[ˈθeɾka] 栅栏&lt;名&gt;</t>
+          <t>[/ˈθeɾka/] 近的；附近&lt;副&gt;（作名词时为“栅栏”）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
@@ -9653,7 +9661,7 @@
       </c>
       <c r="D289" s="1" t="inlineStr">
         <is>
-          <t>栅栏</t>
+          <t>近的；附近&lt;副&gt;（作名词时为“栅栏”）</t>
         </is>
       </c>
       <c r="E289" s="1" t="inlineStr">
@@ -10123,7 +10131,7 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>[ʝeˈɡaɾ] 到达&lt;动&gt;</t>
+          <t>[/ʝeˈɡaɾ/] 到达&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
@@ -10133,7 +10141,7 @@
       </c>
       <c r="D304" s="1" t="inlineStr">
         <is>
-          <t>到达</t>
+          <t>到达&lt;动&gt;</t>
         </is>
       </c>
       <c r="E304" s="1" t="inlineStr">
@@ -10699,7 +10707,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>[iˈɡwal] 一样&lt;名&gt;</t>
+          <t>[/iˈɡwal/] 一样的&lt;形&gt;；相同的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
@@ -10709,7 +10717,7 @@
       </c>
       <c r="D322" s="1" t="inlineStr">
         <is>
-          <t>一样</t>
+          <t>一样的&lt;形&gt;；相同的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E322" s="1" t="inlineStr">
@@ -11147,7 +11155,7 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>[biˈbiɾ] 直播&lt;名&gt;</t>
+          <t>[/biˈbiɾ/] 生活；居住&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
@@ -11157,7 +11165,7 @@
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t>直播</t>
+          <t>生活；居住</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
@@ -11531,7 +11539,7 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t>[ˈabla] 说话&lt;名&gt;</t>
+          <t>[/ˈabla/] 言语；谈话&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
@@ -11541,7 +11549,7 @@
       </c>
       <c r="D348" s="1" t="inlineStr">
         <is>
-          <t>说话</t>
+          <t>言语；谈话&lt;名&gt;</t>
         </is>
       </c>
       <c r="E348" s="1" t="inlineStr">
@@ -11627,7 +11635,7 @@
       </c>
       <c r="B351" s="1" t="inlineStr">
         <is>
-          <t>[aˈtɾas] 回来&lt;副&gt;</t>
+          <t>[/aˈtɾas/] 在后面；向后&lt;adv&gt;</t>
         </is>
       </c>
       <c r="C351" s="1" t="inlineStr">
@@ -11637,7 +11645,7 @@
       </c>
       <c r="D351" s="1" t="inlineStr">
         <is>
-          <t>回来</t>
+          <t>在后面；向后</t>
         </is>
       </c>
       <c r="E351" s="1" t="inlineStr">
@@ -11726,7 +11734,11 @@
           <t>[seˈɲoɾa] 夫人&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C354" s="1" t="inlineStr"/>
+      <c r="C354" s="1" t="inlineStr">
+        <is>
+          <t>/seˈɲoɾa/</t>
+        </is>
+      </c>
       <c r="D354" s="1" t="inlineStr">
         <is>
           <t>夫人。</t>
@@ -12362,7 +12374,11 @@
           <t>[doɡˈtoɾ] 博士&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C374" s="1" t="inlineStr"/>
+      <c r="C374" s="1" t="inlineStr">
+        <is>
+          <t>/doɡˈtoɾ/</t>
+        </is>
+      </c>
       <c r="D374" s="1" t="inlineStr">
         <is>
           <t>博士。</t>
@@ -12803,7 +12819,7 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t>[ˈkeda] 遗骸&lt;名&gt;</t>
+          <t>[/ˈkeda/] 停留；留下&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C388" s="1" t="inlineStr">
@@ -12813,7 +12829,7 @@
       </c>
       <c r="D388" s="1" t="inlineStr">
         <is>
-          <t>遗骸</t>
+          <t>停留；留下</t>
         </is>
       </c>
       <c r="E388" s="1" t="inlineStr">
@@ -13126,7 +13142,11 @@
           <t>你&lt;代&gt;</t>
         </is>
       </c>
-      <c r="C398" s="1" t="inlineStr"/>
+      <c r="C398" s="1" t="inlineStr">
+        <is>
+          <t>/usˈted/</t>
+        </is>
+      </c>
       <c r="D398" s="1" t="inlineStr">
         <is>
           <t>你</t>
@@ -14178,7 +14198,11 @@
           <t>这里&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C431" s="1" t="inlineStr"/>
+      <c r="C431" s="1" t="inlineStr">
+        <is>
+          <t>/akˈi/</t>
+        </is>
+      </c>
       <c r="D431" s="1" t="inlineStr">
         <is>
           <t>这里</t>
@@ -14427,7 +14451,7 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>[ˈoɾden] 订单&lt;名&gt;</t>
+          <t>[/ˈoɾden/] 命令；顺序&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C439" s="1" t="inlineStr">
@@ -14437,7 +14461,7 @@
       </c>
       <c r="D439" s="1" t="inlineStr">
         <is>
-          <t>订单</t>
+          <t>命令；顺序&lt;名&gt;</t>
         </is>
       </c>
       <c r="E439" s="1" t="inlineStr">
@@ -14715,7 +14739,7 @@
       </c>
       <c r="B448" s="1" t="inlineStr">
         <is>
-          <t>[ˈpwesto] 位置&lt;名&gt;</t>
+          <t>[/ˈpwesto/] 地方；岗位；摊位&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C448" s="1" t="inlineStr">
@@ -14725,7 +14749,7 @@
       </c>
       <c r="D448" s="1" t="inlineStr">
         <is>
-          <t>位置</t>
+          <t>地方；岗位；摊位&lt;名&gt;</t>
         </is>
       </c>
       <c r="E448" s="1" t="inlineStr">
@@ -14875,7 +14899,7 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t>[ˈlibɾe] 免费&lt;形&gt;</t>
+          <t>[/ˈlibɾe/] 自由的；免费的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C453" s="1" t="inlineStr">
@@ -14885,7 +14909,7 @@
       </c>
       <c r="D453" s="1" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>自由的；免费的</t>
         </is>
       </c>
       <c r="E453" s="1" t="inlineStr">
@@ -14939,7 +14963,7 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>[soˈnaɾ] 声音&lt;名&gt;</t>
+          <t>[/soˈnaɾ/] 发出声音；响&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C455" s="1" t="inlineStr">
@@ -14949,7 +14973,7 @@
       </c>
       <c r="D455" s="1" t="inlineStr">
         <is>
-          <t>声音</t>
+          <t>发出声音；响</t>
         </is>
       </c>
       <c r="E455" s="1" t="inlineStr">
@@ -15131,7 +15155,7 @@
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t>[ˈresto] 休息&lt;名&gt;</t>
+          <t>[/ˈresto/] 剩余部分；其余&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C461" s="1" t="inlineStr">
@@ -15141,7 +15165,7 @@
       </c>
       <c r="D461" s="1" t="inlineStr">
         <is>
-          <t>休息</t>
+          <t>剩余部分；其余</t>
         </is>
       </c>
       <c r="E461" s="1" t="inlineStr">
@@ -15259,13 +15283,17 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>想念&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C465" s="1" t="inlineStr"/>
+          <t>[[seɲoˈɾita] 小姐&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C465" s="1" t="inlineStr">
+        <is>
+          <t>/ˈseɲoɾita/</t>
+        </is>
+      </c>
       <c r="D465" s="1" t="inlineStr">
         <is>
-          <t>想念</t>
+          <t>小姐</t>
         </is>
       </c>
       <c r="E465" s="1" t="inlineStr">
@@ -17079,7 +17107,7 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>[enkanˈtaɾ] 附魔&lt;动&gt;</t>
+          <t>[/enkanˈtaɾ/] 使喜爱；迷住&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C522" s="1" t="inlineStr">
@@ -17089,7 +17117,7 @@
       </c>
       <c r="D522" s="1" t="inlineStr">
         <is>
-          <t>附魔</t>
+          <t>使喜爱；迷住</t>
         </is>
       </c>
       <c r="E522" s="1" t="inlineStr">
@@ -17175,7 +17203,7 @@
       </c>
       <c r="B525" s="1" t="inlineStr">
         <is>
-          <t>[ˈneɡɾo] 黑色&lt;名&gt;</t>
+          <t>[/ˈneɡɾo/] 黑色的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C525" s="1" t="inlineStr">
@@ -17185,7 +17213,7 @@
       </c>
       <c r="D525" s="1" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>黑色的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E525" s="1" t="inlineStr">
@@ -17431,7 +17459,7 @@
       </c>
       <c r="B533" s="1" t="inlineStr">
         <is>
-          <t>[ˈθita] 报价&lt;名&gt;</t>
+          <t>[/ˈθita/] 约会；预约；引文&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C533" s="1" t="inlineStr">
@@ -17441,7 +17469,7 @@
       </c>
       <c r="D533" s="1" t="inlineStr">
         <is>
-          <t>报价</t>
+          <t>约会；预约；引文</t>
         </is>
       </c>
       <c r="E533" s="1" t="inlineStr">
@@ -17495,7 +17523,7 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡusto] 味道&lt;名&gt;</t>
+          <t>[/ˈɡusto/] 喜好；愉快；兴趣&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C535" s="1" t="inlineStr">
@@ -17505,7 +17533,7 @@
       </c>
       <c r="D535" s="1" t="inlineStr">
         <is>
-          <t>味道</t>
+          <t>喜好；愉快；兴趣&lt;名&gt;</t>
         </is>
       </c>
       <c r="E535" s="1" t="inlineStr">
@@ -18650,7 +18678,11 @@
           <t>所以&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C571" s="1" t="inlineStr"/>
+      <c r="C571" s="1" t="inlineStr">
+        <is>
+          <t>/ˈasi/</t>
+        </is>
+      </c>
       <c r="D571" s="1" t="inlineStr">
         <is>
           <t>所以</t>
@@ -18675,7 +18707,7 @@
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
-          <t>[biˈbaɾ] 直播&lt;动&gt;</t>
+          <t>[/biˈbaɾ/] 生活；居住&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C572" s="1" t="inlineStr">
@@ -18685,7 +18717,7 @@
       </c>
       <c r="D572" s="1" t="inlineStr">
         <is>
-          <t>直播</t>
+          <t>生活；居住</t>
         </is>
       </c>
       <c r="E572" s="1" t="inlineStr">
@@ -18835,7 +18867,7 @@
       </c>
       <c r="B577" s="1" t="inlineStr">
         <is>
-          <t>[ˈdan] 给予&lt;名&gt;</t>
+          <t>[/ˈdan/] dar的第三人称复数现在时（他们给予）&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C577" s="1" t="inlineStr">
@@ -18845,7 +18877,7 @@
       </c>
       <c r="D577" s="1" t="inlineStr">
         <is>
-          <t>给予</t>
+          <t>dar的第三人称复数现在时（他们给予）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E577" s="1" t="inlineStr">
@@ -19027,7 +19059,7 @@
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
-          <t>[ˈsalbo] 已保存&lt;形&gt;</t>
+          <t>[/ˈsalbo/] 除…之外；安然无恙的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C583" s="1" t="inlineStr">
@@ -19037,7 +19069,7 @@
       </c>
       <c r="D583" s="1" t="inlineStr">
         <is>
-          <t>已保存</t>
+          <t>除…之外；安然无恙的</t>
         </is>
       </c>
       <c r="E583" s="1" t="inlineStr">
@@ -19155,7 +19187,7 @@
       </c>
       <c r="B587" s="1" t="inlineStr">
         <is>
-          <t>[ˈmesa] 表&lt;名&gt;</t>
+          <t>[/ˈmesa/] 桌子；餐桌&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C587" s="1" t="inlineStr">
@@ -19165,7 +19197,7 @@
       </c>
       <c r="D587" s="1" t="inlineStr">
         <is>
-          <t>表</t>
+          <t>桌子；餐桌</t>
         </is>
       </c>
       <c r="E587" s="1" t="inlineStr">
@@ -19699,7 +19731,7 @@
       </c>
       <c r="B604" s="1" t="inlineStr">
         <is>
-          <t>[deˈxado] 左&lt;形&gt;</t>
+          <t>[/deˈxado/] 留下的；放弃的；邋遢的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C604" s="1" t="inlineStr">
@@ -19709,7 +19741,7 @@
       </c>
       <c r="D604" s="1" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>留下的；放弃的；邋遢的</t>
         </is>
       </c>
       <c r="E604" s="1" t="inlineStr">
@@ -21110,7 +21142,11 @@
           <t>圣诞节&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C648" s="1" t="inlineStr"/>
+      <c r="C648" s="1" t="inlineStr">
+        <is>
+          <t>/nabiˈðað/</t>
+        </is>
+      </c>
       <c r="D648" s="1" t="inlineStr">
         <is>
           <t>圣诞节</t>
@@ -21231,7 +21267,7 @@
       </c>
       <c r="B652" s="1" t="inlineStr">
         <is>
-          <t>[ˈxuɾo] 我发誓&lt;名&gt;</t>
+          <t>[/ˈxuɾo/] 我发誓&lt;动&gt;（jurar 第一人称单数变位，非名词）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C652" s="1" t="inlineStr">
@@ -21241,7 +21277,7 @@
       </c>
       <c r="D652" s="1" t="inlineStr">
         <is>
-          <t>我发誓</t>
+          <t>我发誓&lt;动&gt;（jurar 第一人称单数变位，非名词）</t>
         </is>
       </c>
       <c r="E652" s="1" t="inlineStr">
@@ -21263,7 +21299,7 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>[manteˈneɾ] 保留&lt;动&gt;</t>
+          <t>[/manteˈneɾ/] 维持；保持&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C653" s="1" t="inlineStr">
@@ -21273,7 +21309,7 @@
       </c>
       <c r="D653" s="1" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持；保持&lt;动&gt;</t>
         </is>
       </c>
       <c r="E653" s="1" t="inlineStr">
@@ -22351,7 +22387,7 @@
       </c>
       <c r="B687" s="1" t="inlineStr">
         <is>
-          <t>[ˈrato] 同时&lt;名&gt;</t>
+          <t>[/ˈrato/] 一会儿；片刻&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C687" s="1" t="inlineStr">
@@ -22361,7 +22397,7 @@
       </c>
       <c r="D687" s="1" t="inlineStr">
         <is>
-          <t>同时</t>
+          <t>一会儿；片刻</t>
         </is>
       </c>
       <c r="E687" s="1" t="inlineStr">
@@ -23188,7 +23224,7 @@
       </c>
       <c r="C713" s="1" t="inlineStr">
         <is>
-          <t>/inteliˈxente/ [ĩn̪.t̪e.liˈxẽn̪.t̪e]</t>
+          <t>/inteliˈxente/</t>
         </is>
       </c>
       <c r="D713" s="1" t="inlineStr">
@@ -23663,7 +23699,7 @@
       </c>
       <c r="B728" s="1" t="inlineStr">
         <is>
-          <t>[ˈkaɾɡo] 收费&lt;名&gt;</t>
+          <t>[/ˈkaɾɡo/] 职位&lt;名&gt;；负载&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C728" s="1" t="inlineStr">
@@ -23673,7 +23709,7 @@
       </c>
       <c r="D728" s="1" t="inlineStr">
         <is>
-          <t>收费</t>
+          <t>职位&lt;名&gt;；负载&lt;名&gt;</t>
         </is>
       </c>
       <c r="E728" s="1" t="inlineStr">
@@ -24559,7 +24595,7 @@
       </c>
       <c r="B756" s="1" t="inlineStr">
         <is>
-          <t>[paɾˈtido] 聚会&lt;名&gt;</t>
+          <t>[/paɾˈtido/] 比赛；政党&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C756" s="1" t="inlineStr">
@@ -24569,7 +24605,7 @@
       </c>
       <c r="D756" s="1" t="inlineStr">
         <is>
-          <t>聚会</t>
+          <t>比赛；政党</t>
         </is>
       </c>
       <c r="E756" s="1" t="inlineStr">
@@ -24943,7 +24979,7 @@
       </c>
       <c r="B768" s="1" t="inlineStr">
         <is>
-          <t>[soˈleɾ] 索莱尔&lt;动&gt;</t>
+          <t>[/soˈleɾ/] 惯于；通常&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C768" s="1" t="inlineStr">
@@ -24953,7 +24989,7 @@
       </c>
       <c r="D768" s="1" t="inlineStr">
         <is>
-          <t>索莱尔</t>
+          <t>惯于；通常</t>
         </is>
       </c>
       <c r="E768" s="1" t="inlineStr">
@@ -25455,7 +25491,7 @@
       </c>
       <c r="B784" s="1" t="inlineStr">
         <is>
-          <t>[esˈpalda] 回来&lt;名&gt;</t>
+          <t>[/esˈpalda/] 背；背部&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C784" s="1" t="inlineStr">
@@ -25465,7 +25501,7 @@
       </c>
       <c r="D784" s="1" t="inlineStr">
         <is>
-          <t>回来</t>
+          <t>背；背部</t>
         </is>
       </c>
       <c r="E784" s="1" t="inlineStr">
@@ -25938,7 +25974,11 @@
           <t>你&lt;代&gt;</t>
         </is>
       </c>
-      <c r="C799" s="1" t="inlineStr"/>
+      <c r="C799" s="1" t="inlineStr">
+        <is>
+          <t>/tˈi/</t>
+        </is>
+      </c>
       <c r="D799" s="1" t="inlineStr">
         <is>
           <t>你</t>
@@ -26411,7 +26451,7 @@
       </c>
       <c r="B814" s="1" t="inlineStr">
         <is>
-          <t>[ˈpista] 轨道&lt;名&gt;</t>
+          <t>[/ˈpista/] 跑道；小路；球场&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C814" s="1" t="inlineStr">
@@ -26421,7 +26461,7 @@
       </c>
       <c r="D814" s="1" t="inlineStr">
         <is>
-          <t>轨道</t>
+          <t>跑道；小路；球场&lt;名&gt;</t>
         </is>
       </c>
       <c r="E814" s="1" t="inlineStr">
@@ -26699,7 +26739,7 @@
       </c>
       <c r="B823" s="1" t="inlineStr">
         <is>
-          <t>[saˈlida] 退出&lt;名&gt;</t>
+          <t>[/saˈlida/] 出口；出发&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C823" s="1" t="inlineStr">
@@ -26709,7 +26749,7 @@
       </c>
       <c r="D823" s="1" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>出口；出发&lt;名&gt;</t>
         </is>
       </c>
       <c r="E823" s="1" t="inlineStr">
@@ -27371,7 +27411,7 @@
       </c>
       <c r="B844" s="1" t="inlineStr">
         <is>
-          <t>[maˈtado] 被杀&lt;形&gt;</t>
+          <t>[/maˈtado/] 被杀的&lt;形&gt;（matar的过去分词）&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C844" s="1" t="inlineStr">
@@ -27381,7 +27421,7 @@
       </c>
       <c r="D844" s="1" t="inlineStr">
         <is>
-          <t>被杀</t>
+          <t>被杀的&lt;形&gt;（matar的过去分词）</t>
         </is>
       </c>
       <c r="E844" s="1" t="inlineStr">
@@ -27819,7 +27859,7 @@
       </c>
       <c r="B858" s="1" t="inlineStr">
         <is>
-          <t>[ˈbob] 鲍勃&lt;名&gt;</t>
+          <t>[/ˈbob/] 傻的；愚蠢的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C858" s="1" t="inlineStr">
@@ -27829,7 +27869,7 @@
       </c>
       <c r="D858" s="1" t="inlineStr">
         <is>
-          <t>鲍勃</t>
+          <t>傻的；愚蠢的</t>
         </is>
       </c>
       <c r="E858" s="1" t="inlineStr">
@@ -27947,7 +27987,7 @@
       </c>
       <c r="B862" s="1" t="inlineStr">
         <is>
-          <t>[esˈtai] 留下来&lt;名&gt;</t>
+          <t>[/esˈtai/] 支索；牵条&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C862" s="1" t="inlineStr">
@@ -27957,7 +27997,7 @@
       </c>
       <c r="D862" s="1" t="inlineStr">
         <is>
-          <t>留下来</t>
+          <t>支索；牵条</t>
         </is>
       </c>
       <c r="E862" s="1" t="inlineStr">
@@ -28075,7 +28115,7 @@
       </c>
       <c r="B866" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡolpe] 吹&lt;名&gt;</t>
+          <t>[/ˈɡolpe/] 打击；一击&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C866" s="1" t="inlineStr">
@@ -28085,7 +28125,7 @@
       </c>
       <c r="D866" s="1" t="inlineStr">
         <is>
-          <t>吹</t>
+          <t>打击；一击</t>
         </is>
       </c>
       <c r="E866" s="1" t="inlineStr">
@@ -28107,7 +28147,7 @@
       </c>
       <c r="B867" s="1" t="inlineStr">
         <is>
-          <t>[akaˈbado] 整理&lt;名&gt;</t>
+          <t>[/akaˈbado/] 完成的；结束的；饰面&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C867" s="1" t="inlineStr">
@@ -28117,7 +28157,7 @@
       </c>
       <c r="D867" s="1" t="inlineStr">
         <is>
-          <t>整理</t>
+          <t>完成的；结束的；饰面</t>
         </is>
       </c>
       <c r="E867" s="1" t="inlineStr">
@@ -28587,7 +28627,7 @@
       </c>
       <c r="B882" s="1" t="inlineStr">
         <is>
-          <t>[ˈsuʝo] 你的&lt;代&gt;</t>
+          <t>[/ˈsuʝo/] 他的；她的；他们的；您的&lt;pron&gt;</t>
         </is>
       </c>
       <c r="C882" s="1" t="inlineStr">
@@ -28597,7 +28637,7 @@
       </c>
       <c r="D882" s="1" t="inlineStr">
         <is>
-          <t>你的</t>
+          <t>他的；她的；他们的；您的</t>
         </is>
       </c>
       <c r="E882" s="1" t="inlineStr">
@@ -28651,7 +28691,7 @@
       </c>
       <c r="B884" s="1" t="inlineStr">
         <is>
-          <t>[reˈpente] 突然&lt;名&gt;</t>
+          <t>[/reˈpente/] 突然&lt;副&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C884" s="1" t="inlineStr">
@@ -28661,7 +28701,7 @@
       </c>
       <c r="D884" s="1" t="inlineStr">
         <is>
-          <t>突然</t>
+          <t>突然&lt;副&gt;</t>
         </is>
       </c>
       <c r="E884" s="1" t="inlineStr">
@@ -29035,7 +29075,7 @@
       </c>
       <c r="B896" s="1" t="inlineStr">
         <is>
-          <t>[ˈama] 爱&lt;名&gt;</t>
+          <t>[/ˈama/] 女主人；主妇&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C896" s="1" t="inlineStr">
@@ -29045,7 +29085,7 @@
       </c>
       <c r="D896" s="1" t="inlineStr">
         <is>
-          <t>爱</t>
+          <t>女主人；主妇</t>
         </is>
       </c>
       <c r="E896" s="1" t="inlineStr">
@@ -30187,7 +30227,7 @@
       </c>
       <c r="B932" s="1" t="inlineStr">
         <is>
-          <t>[ˈblanka] 白色&lt;名&gt;</t>
+          <t>[/ˈblanka/] 白色的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C932" s="1" t="inlineStr">
@@ -30197,7 +30237,7 @@
       </c>
       <c r="D932" s="1" t="inlineStr">
         <is>
-          <t>白色</t>
+          <t>白色的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E932" s="1" t="inlineStr">
@@ -30699,7 +30739,7 @@
       </c>
       <c r="B948" s="1" t="inlineStr">
         <is>
-          <t>[saˈlido] 退出&lt;形&gt;</t>
+          <t>[/saˈlido/] 好色的；放荡的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C948" s="1" t="inlineStr">
@@ -30709,7 +30749,7 @@
       </c>
       <c r="D948" s="1" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>好色的；放荡的</t>
         </is>
       </c>
       <c r="E948" s="1" t="inlineStr">
@@ -31275,7 +31315,7 @@
       </c>
       <c r="B966" s="1" t="inlineStr">
         <is>
-          <t>[riˈdikulo] 可笑&lt;名&gt;</t>
+          <t>[/riˈdikulo/] 可笑的&lt;形&gt;；可笑的事&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C966" s="1" t="inlineStr">
@@ -31285,7 +31325,7 @@
       </c>
       <c r="D966" s="1" t="inlineStr">
         <is>
-          <t>可笑</t>
+          <t>可笑的&lt;形&gt;；可笑的事&lt;名&gt;</t>
         </is>
       </c>
       <c r="E966" s="1" t="inlineStr">
@@ -31339,7 +31379,7 @@
       </c>
       <c r="B968" s="1" t="inlineStr">
         <is>
-          <t>[opeɾaˈθjon] 操作&lt;名&gt;</t>
+          <t>[/opeɾaˈθjon/] 手术；操作&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C968" s="1" t="inlineStr">
@@ -31349,7 +31389,7 @@
       </c>
       <c r="D968" s="1" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>手术；操作&lt;名&gt;</t>
         </is>
       </c>
       <c r="E968" s="1" t="inlineStr">
@@ -31883,7 +31923,7 @@
       </c>
       <c r="B985" s="1" t="inlineStr">
         <is>
-          <t>[konˈtɾaɾjo] 对面&lt;形&gt;</t>
+          <t>[/konˈtɾaɾjo/] 相反的；反对的；对手&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C985" s="1" t="inlineStr">
@@ -31893,7 +31933,7 @@
       </c>
       <c r="D985" s="1" t="inlineStr">
         <is>
-          <t>对面</t>
+          <t>相反的；反对的；对手</t>
         </is>
       </c>
       <c r="E985" s="1" t="inlineStr">
@@ -32107,7 +32147,7 @@
       </c>
       <c r="B992" s="1" t="inlineStr">
         <is>
-          <t>[bjembeˈnida] 欢迎&lt;名&gt;</t>
+          <t>[/bjembeˈnida/] 欢迎&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C992" s="1" t="inlineStr">
@@ -32117,7 +32157,7 @@
       </c>
       <c r="D992" s="1" t="inlineStr">
         <is>
-          <t>欢迎</t>
+          <t>欢迎&lt;名&gt;</t>
         </is>
       </c>
       <c r="E992" s="1" t="inlineStr">
@@ -32139,7 +32179,7 @@
       </c>
       <c r="B993" s="1" t="inlineStr">
         <is>
-          <t>[kaˈeɾ] 秋天&lt;动&gt;</t>
+          <t>[/kaˈeɾ/] 落下；掉落；跌倒&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C993" s="1" t="inlineStr">
@@ -32149,7 +32189,7 @@
       </c>
       <c r="D993" s="1" t="inlineStr">
         <is>
-          <t>秋天</t>
+          <t>落下；掉落；跌倒</t>
         </is>
       </c>
       <c r="E993" s="1" t="inlineStr">
@@ -32459,7 +32499,7 @@
       </c>
       <c r="B1003" s="1" t="inlineStr">
         <is>
-          <t>[deθiˈdido] 决定&lt;形&gt;</t>
+          <t>[/deθiˈdido/] 坚决的；果断的；已决定的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1003" s="1" t="inlineStr">
@@ -32469,7 +32509,7 @@
       </c>
       <c r="D1003" s="1" t="inlineStr">
         <is>
-          <t>决定</t>
+          <t>坚决的；果断的；已决定的</t>
         </is>
       </c>
       <c r="E1003" s="1" t="inlineStr">
@@ -33323,7 +33363,7 @@
       </c>
       <c r="B1030" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾensa] 按&lt;名&gt;</t>
+          <t>[/ˈpɾensa/] 新闻界；媒体；印刷机&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1030" s="1" t="inlineStr">
@@ -33333,7 +33373,7 @@
       </c>
       <c r="D1030" s="1" t="inlineStr">
         <is>
-          <t>按</t>
+          <t>新闻界；媒体；印刷机</t>
         </is>
       </c>
       <c r="E1030" s="1" t="inlineStr">
@@ -33995,7 +34035,7 @@
       </c>
       <c r="B1051" s="1" t="inlineStr">
         <is>
-          <t>[ˈbebe] 宝贝&lt;名&gt;</t>
+          <t>[/ˈbebe/] 喝&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1051" s="1" t="inlineStr">
@@ -34005,7 +34045,7 @@
       </c>
       <c r="D1051" s="1" t="inlineStr">
         <is>
-          <t>宝贝</t>
+          <t>喝&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1051" s="1" t="inlineStr">
@@ -34027,7 +34067,7 @@
       </c>
       <c r="B1052" s="1" t="inlineStr">
         <is>
-          <t>[ˈpapa] 爸爸&lt;名&gt;</t>
+          <t>[/ˈpapa/] 土豆&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1052" s="1" t="inlineStr">
@@ -34037,7 +34077,7 @@
       </c>
       <c r="D1052" s="1" t="inlineStr">
         <is>
-          <t>爸爸</t>
+          <t>土豆&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1052" s="1" t="inlineStr">
@@ -34091,7 +34131,7 @@
       </c>
       <c r="B1054" s="1" t="inlineStr">
         <is>
-          <t>[famiˈljaɾ] 家庭&lt;名&gt;</t>
+          <t>[/famiˈljaɾ/] 家庭的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1054" s="1" t="inlineStr">
@@ -34101,7 +34141,7 @@
       </c>
       <c r="D1054" s="1" t="inlineStr">
         <is>
-          <t>家庭</t>
+          <t>家庭的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1054" s="1" t="inlineStr">
@@ -34507,7 +34547,7 @@
       </c>
       <c r="B1067" s="1" t="inlineStr">
         <is>
-          <t>[kanˈtaɾ] 唱歌&lt;名&gt;</t>
+          <t>[/kanˈtaɾ/] 唱歌&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1067" s="1" t="inlineStr">
@@ -34517,7 +34557,7 @@
       </c>
       <c r="D1067" s="1" t="inlineStr">
         <is>
-          <t>唱歌</t>
+          <t>唱歌&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1067" s="1" t="inlineStr">
@@ -34731,7 +34771,7 @@
       </c>
       <c r="B1074" s="1" t="inlineStr">
         <is>
-          <t>[esˈtan] 是&lt;动&gt;</t>
+          <t>[/esˈtan/] （他们）在，处于（estar的第三人称复数变位）&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1074" s="1" t="inlineStr">
@@ -34741,7 +34781,7 @@
       </c>
       <c r="D1074" s="1" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>（他们）在，处于（estar的第三人称复数变位）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1074" s="1" t="inlineStr">
@@ -34891,7 +34931,7 @@
       </c>
       <c r="B1079" s="1" t="inlineStr">
         <is>
-          <t>[ˈʃow] 显示&lt;名&gt;</t>
+          <t>[/ˈʃow/] 演出，表演&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1079" s="1" t="inlineStr">
@@ -34901,7 +34941,7 @@
       </c>
       <c r="D1079" s="1" t="inlineStr">
         <is>
-          <t>显示</t>
+          <t>演出，表演&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1079" s="1" t="inlineStr">
@@ -35019,13 +35059,17 @@
       </c>
       <c r="B1083" s="1" t="inlineStr">
         <is>
-          <t>你&lt;代&gt;</t>
-        </is>
-      </c>
-      <c r="C1083" s="1" t="inlineStr"/>
+          <t>[[usˈteðes] 你们；诸位&lt;pron&gt;</t>
+        </is>
+      </c>
+      <c r="C1083" s="1" t="inlineStr">
+        <is>
+          <t>/usˈtedes/</t>
+        </is>
+      </c>
       <c r="D1083" s="1" t="inlineStr">
         <is>
-          <t>你</t>
+          <t>你们；诸位</t>
         </is>
       </c>
       <c r="E1083" s="1" t="inlineStr">
@@ -35591,7 +35635,7 @@
       </c>
       <c r="B1101" s="1" t="inlineStr">
         <is>
-          <t>[eˈt͡ʃaɾ] 演员表&lt;动&gt;</t>
+          <t>[/eˈt͡ʃaɾ/] 扔；投掷；抛出&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1101" s="1" t="inlineStr">
@@ -35601,7 +35645,7 @@
       </c>
       <c r="D1101" s="1" t="inlineStr">
         <is>
-          <t>演员表</t>
+          <t>扔；投掷；抛出</t>
         </is>
       </c>
       <c r="E1101" s="1" t="inlineStr">
@@ -35751,7 +35795,7 @@
       </c>
       <c r="B1106" s="1" t="inlineStr">
         <is>
-          <t>[espeɡˈtakulo] 显示&lt;名&gt;</t>
+          <t>[/espeɡˈtakulo/] 演出；表演；景象&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1106" s="1" t="inlineStr">
@@ -35761,7 +35805,7 @@
       </c>
       <c r="D1106" s="1" t="inlineStr">
         <is>
-          <t>显示</t>
+          <t>演出；表演；景象</t>
         </is>
       </c>
       <c r="E1106" s="1" t="inlineStr">
@@ -36231,7 +36275,7 @@
       </c>
       <c r="B1121" s="1" t="inlineStr">
         <is>
-          <t>[aˈbjeɾto] 打开&lt;名&gt;</t>
+          <t>[/aˈbjeɾto/] 开着的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1121" s="1" t="inlineStr">
@@ -36241,7 +36285,7 @@
       </c>
       <c r="D1121" s="1" t="inlineStr">
         <is>
-          <t>打开</t>
+          <t>开着的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1121" s="1" t="inlineStr">
@@ -36391,7 +36435,7 @@
       </c>
       <c r="B1126" s="1" t="inlineStr">
         <is>
-          <t>[boˈrat͡ʃo] 喝醉了&lt;名&gt;</t>
+          <t>[/boˈrat͡ʃo/] 喝醉的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1126" s="1" t="inlineStr">
@@ -36401,7 +36445,7 @@
       </c>
       <c r="D1126" s="1" t="inlineStr">
         <is>
-          <t>喝醉了</t>
+          <t>喝醉的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1126" s="1" t="inlineStr">
@@ -36487,7 +36531,7 @@
       </c>
       <c r="B1129" s="1" t="inlineStr">
         <is>
-          <t>[ˈeɡs] 前&lt;名&gt;</t>
+          <t>[/ˈeɡs/] 前任&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1129" s="1" t="inlineStr">
@@ -36497,7 +36541,7 @@
       </c>
       <c r="D1129" s="1" t="inlineStr">
         <is>
-          <t>前</t>
+          <t>前任&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1129" s="1" t="inlineStr">
@@ -36554,7 +36598,11 @@
           <t>[doɡˈtoɾa] 博士&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1131" s="1" t="inlineStr"/>
+      <c r="C1131" s="1" t="inlineStr">
+        <is>
+          <t>/doɡˈtoɾa/</t>
+        </is>
+      </c>
       <c r="D1131" s="1" t="inlineStr">
         <is>
           <t>博士。</t>
@@ -36611,7 +36659,7 @@
       </c>
       <c r="B1133" s="1" t="inlineStr">
         <is>
-          <t>[ˈputo] 他妈的&lt;名&gt;</t>
+          <t>[/ˈputo/] 该死的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1133" s="1" t="inlineStr">
@@ -36621,7 +36669,7 @@
       </c>
       <c r="D1133" s="1" t="inlineStr">
         <is>
-          <t>他妈的</t>
+          <t>该死的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1133" s="1" t="inlineStr">
@@ -36835,7 +36883,7 @@
       </c>
       <c r="B1140" s="1" t="inlineStr">
         <is>
-          <t>[aɡɾadeˈθeɾ] 谢谢你&lt;动&gt;</t>
+          <t>[/aɡɾadeˈθeɾ/] 感谢&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1140" s="1" t="inlineStr">
@@ -36845,7 +36893,7 @@
       </c>
       <c r="D1140" s="1" t="inlineStr">
         <is>
-          <t>谢谢你</t>
+          <t>感谢&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1140" s="1" t="inlineStr">
@@ -37350,7 +37398,11 @@
           <t>那里&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C1156" s="1" t="inlineStr"/>
+      <c r="C1156" s="1" t="inlineStr">
+        <is>
+          <t>/ˈai/</t>
+        </is>
+      </c>
       <c r="D1156" s="1" t="inlineStr">
         <is>
           <t>那里</t>
@@ -37599,7 +37651,7 @@
       </c>
       <c r="B1164" s="1" t="inlineStr">
         <is>
-          <t>[ˈleo] 狮子座&lt;名&gt;</t>
+          <t>[/ˈleo/] 我读（leer的第一人称单数现在式）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1164" s="1" t="inlineStr">
@@ -37609,7 +37661,7 @@
       </c>
       <c r="D1164" s="1" t="inlineStr">
         <is>
-          <t>狮子座</t>
+          <t>我读（leer的第一人称单数现在式）</t>
         </is>
       </c>
       <c r="E1164" s="1" t="inlineStr">
@@ -38623,7 +38675,7 @@
       </c>
       <c r="B1196" s="1" t="inlineStr">
         <is>
-          <t>[menˈtiɾ] 谎言&lt;动&gt;</t>
+          <t>[/menˈtiɾ/] 说谎；撒谎&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1196" s="1" t="inlineStr">
@@ -38633,7 +38685,7 @@
       </c>
       <c r="D1196" s="1" t="inlineStr">
         <is>
-          <t>谎言</t>
+          <t>说谎；撒谎</t>
         </is>
       </c>
       <c r="E1196" s="1" t="inlineStr">
@@ -38975,13 +39027,17 @@
       </c>
       <c r="B1207" s="1" t="inlineStr">
         <is>
-          <t>到&lt;叹&gt;</t>
-        </is>
-      </c>
-      <c r="C1207" s="1" t="inlineStr"/>
+          <t>[[ˈto] 到；向；对于&lt;intj&gt;</t>
+        </is>
+      </c>
+      <c r="C1207" s="1" t="inlineStr">
+        <is>
+          <t>/tˈo/</t>
+        </is>
+      </c>
       <c r="D1207" s="1" t="inlineStr">
         <is>
-          <t>到</t>
+          <t>到；向；对于</t>
         </is>
       </c>
       <c r="E1207" s="1" t="inlineStr">
@@ -39035,7 +39091,7 @@
       </c>
       <c r="B1209" s="1" t="inlineStr">
         <is>
-          <t>[ˈt͡ʃina] 中国人&lt;名&gt;</t>
+          <t>[/ˈt͡ʃina/] 中国人（女）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1209" s="1" t="inlineStr">
@@ -39045,7 +39101,7 @@
       </c>
       <c r="D1209" s="1" t="inlineStr">
         <is>
-          <t>中国人</t>
+          <t>中国人（女）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1209" s="1" t="inlineStr">
@@ -39387,7 +39443,7 @@
       </c>
       <c r="B1220" s="1" t="inlineStr">
         <is>
-          <t>[oˈleɾ] 气味&lt;动&gt;</t>
+          <t>[/oˈleɾ/] 闻；嗅；散发气味&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1220" s="1" t="inlineStr">
@@ -39397,7 +39453,7 @@
       </c>
       <c r="D1220" s="1" t="inlineStr">
         <is>
-          <t>气味</t>
+          <t>闻；嗅；散发气味</t>
         </is>
       </c>
       <c r="E1220" s="1" t="inlineStr">
@@ -39707,7 +39763,7 @@
       </c>
       <c r="B1230" s="1" t="inlineStr">
         <is>
-          <t>[lebanˈtaɾ] 电梯&lt;动&gt;</t>
+          <t>[/lebanˈtaɾ/] 举起；抬起；升起&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1230" s="1" t="inlineStr">
@@ -39717,7 +39773,7 @@
       </c>
       <c r="D1230" s="1" t="inlineStr">
         <is>
-          <t>电梯</t>
+          <t>举起；抬起；升起</t>
         </is>
       </c>
       <c r="E1230" s="1" t="inlineStr">
@@ -39995,7 +40051,7 @@
       </c>
       <c r="B1239" s="1" t="inlineStr">
         <is>
-          <t>[bolunˈtad] 会&lt;名&gt;</t>
+          <t>[/bolunˈtad/] 意志；意愿&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1239" s="1" t="inlineStr">
@@ -40005,7 +40061,7 @@
       </c>
       <c r="D1239" s="1" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>意志；意愿</t>
         </is>
       </c>
       <c r="E1239" s="1" t="inlineStr">
@@ -40347,7 +40403,7 @@
       </c>
       <c r="B1250" s="1" t="inlineStr">
         <is>
-          <t>[meˈtido] 把&lt;形&gt;</t>
+          <t>[/meˈtido/] 介入的；参与的；多管闲事的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1250" s="1" t="inlineStr">
@@ -40357,7 +40413,7 @@
       </c>
       <c r="D1250" s="1" t="inlineStr">
         <is>
-          <t>把</t>
+          <t>介入的；参与的；多管闲事的</t>
         </is>
       </c>
       <c r="E1250" s="1" t="inlineStr">
@@ -40571,7 +40627,7 @@
       </c>
       <c r="B1257" s="1" t="inlineStr">
         <is>
-          <t>[kareˈteɾo] 卡特&lt;名&gt;</t>
+          <t>[/kareˈteɾo/] 车夫；赶车人&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1257" s="1" t="inlineStr">
@@ -40581,7 +40637,7 @@
       </c>
       <c r="D1257" s="1" t="inlineStr">
         <is>
-          <t>卡特</t>
+          <t>车夫；赶车人</t>
         </is>
       </c>
       <c r="E1257" s="1" t="inlineStr">
@@ -40766,7 +40822,11 @@
           <t>也&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C1263" s="1" t="inlineStr"/>
+      <c r="C1263" s="1" t="inlineStr">
+        <is>
+          <t>/tambˈien/</t>
+        </is>
+      </c>
       <c r="D1263" s="1" t="inlineStr">
         <is>
           <t>也</t>
@@ -40858,7 +40918,11 @@
           <t>先生&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1266" s="1" t="inlineStr"/>
+      <c r="C1266" s="1" t="inlineStr">
+        <is>
+          <t>/seˈɲoɾ/</t>
+        </is>
+      </c>
       <c r="D1266" s="1" t="inlineStr">
         <is>
           <t>先生</t>
@@ -41043,7 +41107,7 @@
       </c>
       <c r="B1272" s="1" t="inlineStr">
         <is>
-          <t>[limˈpjaɾ] 干净&lt;动&gt;</t>
+          <t>[/limˈpjaɾ/] 打扫；清洗；清洁&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1272" s="1" t="inlineStr">
@@ -41053,7 +41117,7 @@
       </c>
       <c r="D1272" s="1" t="inlineStr">
         <is>
-          <t>干净</t>
+          <t>打扫；清洗；清洁</t>
         </is>
       </c>
       <c r="E1272" s="1" t="inlineStr">
@@ -42259,7 +42323,7 @@
       </c>
       <c r="B1310" s="1" t="inlineStr">
         <is>
-          <t>[taˈlento] 人才&lt;名&gt;</t>
+          <t>[/taˈlento/] 才能；天才&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1310" s="1" t="inlineStr">
@@ -42269,7 +42333,7 @@
       </c>
       <c r="D1310" s="1" t="inlineStr">
         <is>
-          <t>人才</t>
+          <t>才能；天才&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1310" s="1" t="inlineStr">
@@ -42323,7 +42387,7 @@
       </c>
       <c r="B1312" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡoɾdo] 脂肪&lt;名&gt;</t>
+          <t>[/ˈɡoɾdo/] 胖的；肥胖的；胖子&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1312" s="1" t="inlineStr">
@@ -42333,7 +42397,7 @@
       </c>
       <c r="D1312" s="1" t="inlineStr">
         <is>
-          <t>脂肪</t>
+          <t>胖的；肥胖的；胖子</t>
         </is>
       </c>
       <c r="E1312" s="1" t="inlineStr">
@@ -42771,13 +42835,17 @@
       </c>
       <c r="B1326" s="1" t="inlineStr">
         <is>
-          <t>去了&lt;动&gt;</t>
-        </is>
-      </c>
-      <c r="C1326" s="1" t="inlineStr"/>
+          <t>[[ˈfwe] 是；去了（ser/ir的过去时第三人称单数）&lt;verb&gt;</t>
+        </is>
+      </c>
+      <c r="C1326" s="1" t="inlineStr">
+        <is>
+          <t>/fuˈe/</t>
+        </is>
+      </c>
       <c r="D1326" s="1" t="inlineStr">
         <is>
-          <t>去了</t>
+          <t>是；去了（ser/ir的过去时第三人称单数）</t>
         </is>
       </c>
       <c r="E1326" s="1" t="inlineStr">
@@ -42898,7 +42966,11 @@
           <t>日&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1330" s="1" t="inlineStr"/>
+      <c r="C1330" s="1" t="inlineStr">
+        <is>
+          <t>/dˈia/</t>
+        </is>
+      </c>
       <c r="D1330" s="1" t="inlineStr">
         <is>
           <t>日</t>
@@ -43755,7 +43827,7 @@
       </c>
       <c r="B1357" s="1" t="inlineStr">
         <is>
-          <t>[ˈsaka] 拿出来&lt;名&gt;</t>
+          <t>[/ˈsaka/] 袋，包&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1357" s="1" t="inlineStr">
@@ -43765,7 +43837,7 @@
       </c>
       <c r="D1357" s="1" t="inlineStr">
         <is>
-          <t>拿出来</t>
+          <t>袋，包&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1357" s="1" t="inlineStr">
@@ -43915,7 +43987,7 @@
       </c>
       <c r="B1362" s="1" t="inlineStr">
         <is>
-          <t>[ˈθjento] 分&lt;名&gt;</t>
+          <t>[/ˈθjento/] 百&lt;数&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1362" s="1" t="inlineStr">
@@ -43925,7 +43997,7 @@
       </c>
       <c r="D1362" s="1" t="inlineStr">
         <is>
-          <t>分</t>
+          <t>百&lt;数&gt;</t>
         </is>
       </c>
       <c r="E1362" s="1" t="inlineStr">
@@ -44299,7 +44371,7 @@
       </c>
       <c r="B1374" s="1" t="inlineStr">
         <is>
-          <t>[kaˈsaɾ] 结婚&lt;动&gt;</t>
+          <t>[/kaˈsaɾ/] 嫁娶；为…主持婚礼&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1374" s="1" t="inlineStr">
@@ -44309,7 +44381,7 @@
       </c>
       <c r="D1374" s="1" t="inlineStr">
         <is>
-          <t>结婚</t>
+          <t>嫁娶；为…主持婚礼&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1374" s="1" t="inlineStr">
@@ -44331,7 +44403,7 @@
       </c>
       <c r="B1375" s="1" t="inlineStr">
         <is>
-          <t>[beˈbida] 喝&lt;名&gt;</t>
+          <t>[/beˈbida/] 饮料；饮品&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1375" s="1" t="inlineStr">
@@ -44341,7 +44413,7 @@
       </c>
       <c r="D1375" s="1" t="inlineStr">
         <is>
-          <t>喝</t>
+          <t>饮料；饮品</t>
         </is>
       </c>
       <c r="E1375" s="1" t="inlineStr">
@@ -45195,13 +45267,17 @@
       </c>
       <c r="B1402" s="1" t="inlineStr">
         <is>
-          <t>瀑布&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1402" s="1" t="inlineStr"/>
+          <t>[[ˈka.e] 落下；跌倒（caer的第三人称单数）&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1402" s="1" t="inlineStr">
+        <is>
+          <t>/ˈkae/</t>
+        </is>
+      </c>
       <c r="D1402" s="1" t="inlineStr">
         <is>
-          <t>瀑布</t>
+          <t>落下；跌倒（caer的第三人称单数）</t>
         </is>
       </c>
       <c r="E1402" s="1" t="inlineStr">
@@ -45287,7 +45363,7 @@
       </c>
       <c r="B1405" s="1" t="inlineStr">
         <is>
-          <t>[ˈkjeto] 仍然&lt;形&gt;</t>
+          <t>[/ˈkjeto/] 静止的；不动的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1405" s="1" t="inlineStr">
@@ -45297,7 +45373,7 @@
       </c>
       <c r="D1405" s="1" t="inlineStr">
         <is>
-          <t>仍然</t>
+          <t>静止的；不动的</t>
         </is>
       </c>
       <c r="E1405" s="1" t="inlineStr">
@@ -46151,7 +46227,7 @@
       </c>
       <c r="B1432" s="1" t="inlineStr">
         <is>
-          <t>[ˈdes] 德斯&lt;介&gt;</t>
+          <t>[/ˈdes/] （前缀）表示否定、分离、去除&lt;prep&gt;</t>
         </is>
       </c>
       <c r="C1432" s="1" t="inlineStr">
@@ -46161,7 +46237,7 @@
       </c>
       <c r="D1432" s="1" t="inlineStr">
         <is>
-          <t>德斯</t>
+          <t>（前缀）表示否定、分离、去除</t>
         </is>
       </c>
       <c r="E1432" s="1" t="inlineStr">
@@ -46186,7 +46262,11 @@
           <t>技术&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1433" s="1" t="inlineStr"/>
+      <c r="C1433" s="1" t="inlineStr">
+        <is>
+          <t>/texnoloˈxia/</t>
+        </is>
+      </c>
       <c r="D1433" s="1" t="inlineStr">
         <is>
           <t>技术</t>
@@ -46371,7 +46451,7 @@
       </c>
       <c r="B1439" s="1" t="inlineStr">
         <is>
-          <t>[ˈboɾdo] 董事会&lt;名&gt;</t>
+          <t>[/ˈboɾdo/] 边缘；船舷&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1439" s="1" t="inlineStr">
@@ -46381,7 +46461,7 @@
       </c>
       <c r="D1439" s="1" t="inlineStr">
         <is>
-          <t>董事会</t>
+          <t>边缘；船舷</t>
         </is>
       </c>
       <c r="E1439" s="1" t="inlineStr">
@@ -47075,7 +47155,7 @@
       </c>
       <c r="B1461" s="1" t="inlineStr">
         <is>
-          <t>[kaliˈfoɾnjo] 加利福尼亚州&lt;名&gt;</t>
+          <t>[/kaliˈfoɾnjo/] 锎（化学元素）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1461" s="1" t="inlineStr">
@@ -47085,7 +47165,7 @@
       </c>
       <c r="D1461" s="1" t="inlineStr">
         <is>
-          <t>加利福尼亚州</t>
+          <t>锎（化学元素）</t>
         </is>
       </c>
       <c r="E1461" s="1" t="inlineStr">
@@ -49030,7 +49110,11 @@
           <t>之后&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C1522" s="1" t="inlineStr"/>
+      <c r="C1522" s="1" t="inlineStr">
+        <is>
+          <t>/despˈues/</t>
+        </is>
+      </c>
       <c r="D1522" s="1" t="inlineStr">
         <is>
           <t>之后</t>
@@ -49983,7 +50067,7 @@
       </c>
       <c r="B1552" s="1" t="inlineStr">
         <is>
-          <t>[diskulˈpaɾ] 借口&lt;动&gt;</t>
+          <t>[/diskulˈpaɾ/] 原谅；道歉&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1552" s="1" t="inlineStr">
@@ -49993,7 +50077,7 @@
       </c>
       <c r="D1552" s="1" t="inlineStr">
         <is>
-          <t>借口</t>
+          <t>原谅；道歉</t>
         </is>
       </c>
       <c r="E1552" s="1" t="inlineStr">
@@ -50111,7 +50195,7 @@
       </c>
       <c r="B1556" s="1" t="inlineStr">
         <is>
-          <t>[ˈbaso] 玻璃&lt;名&gt;</t>
+          <t>[/ˈbaso/] 杯子；玻璃杯&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1556" s="1" t="inlineStr">
@@ -50121,7 +50205,7 @@
       </c>
       <c r="D1556" s="1" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>杯子；玻璃杯</t>
         </is>
       </c>
       <c r="E1556" s="1" t="inlineStr">
@@ -50815,7 +50899,7 @@
       </c>
       <c r="B1578" s="1" t="inlineStr">
         <is>
-          <t>[aleˈxaɾ] 缩小&lt;动&gt;</t>
+          <t>[/aleˈxaɾ/] 使远离；使疏远&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1578" s="1" t="inlineStr">
@@ -50825,7 +50909,7 @@
       </c>
       <c r="D1578" s="1" t="inlineStr">
         <is>
-          <t>缩小</t>
+          <t>使远离；使疏远</t>
         </is>
       </c>
       <c r="E1578" s="1" t="inlineStr">
@@ -51071,7 +51155,7 @@
       </c>
       <c r="B1586" s="1" t="inlineStr">
         <is>
-          <t>[ˈmiɾ] 看看&lt;名&gt;</t>
+          <t>[/ˈmiɾ/] 看；注视&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1586" s="1" t="inlineStr">
@@ -51081,7 +51165,7 @@
       </c>
       <c r="D1586" s="1" t="inlineStr">
         <is>
-          <t>看看</t>
+          <t>看；注视</t>
         </is>
       </c>
       <c r="E1586" s="1" t="inlineStr">
@@ -51647,7 +51731,7 @@
       </c>
       <c r="B1604" s="1" t="inlineStr">
         <is>
-          <t>[konˈsiɡo] 我明白了&lt;副&gt;</t>
+          <t>[/konˈsiɡo/] 随身；和自己一起&lt;adv&gt;</t>
         </is>
       </c>
       <c r="C1604" s="1" t="inlineStr">
@@ -51657,7 +51741,7 @@
       </c>
       <c r="D1604" s="1" t="inlineStr">
         <is>
-          <t>我明白了</t>
+          <t>随身；和自己一起</t>
         </is>
       </c>
       <c r="E1604" s="1" t="inlineStr">
@@ -51807,7 +51891,7 @@
       </c>
       <c r="B1609" s="1" t="inlineStr">
         <is>
-          <t>[maˈɾina] 海军&lt;名&gt;</t>
+          <t>[/maˈɾina/] 海事的；海军的；海滨&lt;形/名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1609" s="1" t="inlineStr">
@@ -51817,7 +51901,7 @@
       </c>
       <c r="D1609" s="1" t="inlineStr">
         <is>
-          <t>海军</t>
+          <t>海事的；海军的；海滨&lt;形/名&gt;</t>
         </is>
       </c>
       <c r="E1609" s="1" t="inlineStr">
@@ -51999,7 +52083,7 @@
       </c>
       <c r="B1615" s="1" t="inlineStr">
         <is>
-          <t>[ˈt͡ʃeke] 检查&lt;名&gt;</t>
+          <t>[/ˈt͡ʃeke/] 支票&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1615" s="1" t="inlineStr">
@@ -52009,7 +52093,7 @@
       </c>
       <c r="D1615" s="1" t="inlineStr">
         <is>
-          <t>检查</t>
+          <t>支票</t>
         </is>
       </c>
       <c r="E1615" s="1" t="inlineStr">
@@ -53090,7 +53174,11 @@
           <t>你&lt;代&gt;</t>
         </is>
       </c>
-      <c r="C1649" s="1" t="inlineStr"/>
+      <c r="C1649" s="1" t="inlineStr">
+        <is>
+          <t>/usˈted/</t>
+        </is>
+      </c>
       <c r="D1649" s="1" t="inlineStr">
         <is>
           <t>你</t>
@@ -53115,7 +53203,7 @@
       </c>
       <c r="B1650" s="1" t="inlineStr">
         <is>
-          <t>[impɾeˈsjon] 打印&lt;名&gt;</t>
+          <t>[/impɾeˈsjon/] 印刷；印象&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1650" s="1" t="inlineStr">
@@ -53125,7 +53213,7 @@
       </c>
       <c r="D1650" s="1" t="inlineStr">
         <is>
-          <t>打印</t>
+          <t>印刷；印象&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1650" s="1" t="inlineStr">
@@ -53243,7 +53331,7 @@
       </c>
       <c r="B1654" s="1" t="inlineStr">
         <is>
-          <t>[solˈtaɾ] 掉落&lt;动&gt;</t>
+          <t>[/solˈtaɾ/] 松开；放开；释放&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1654" s="1" t="inlineStr">
@@ -53253,7 +53341,7 @@
       </c>
       <c r="D1654" s="1" t="inlineStr">
         <is>
-          <t>掉落</t>
+          <t>松开；放开；释放</t>
         </is>
       </c>
       <c r="E1654" s="1" t="inlineStr">
@@ -53435,7 +53523,7 @@
       </c>
       <c r="B1660" s="1" t="inlineStr">
         <is>
-          <t>[pɾesenˈtaɾ] 现在&lt;动&gt;</t>
+          <t>[/pɾesenˈtaɾ/] 介绍；提出；呈现&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1660" s="1" t="inlineStr">
@@ -53445,7 +53533,7 @@
       </c>
       <c r="D1660" s="1" t="inlineStr">
         <is>
-          <t>现在</t>
+          <t>介绍；提出；呈现</t>
         </is>
       </c>
       <c r="E1660" s="1" t="inlineStr">
@@ -53499,7 +53587,7 @@
       </c>
       <c r="B1662" s="1" t="inlineStr">
         <is>
-          <t>[laɾˈɡaɾ] 离开&lt;动&gt;</t>
+          <t>[/laɾˈɡaɾ/] 松开；放出；（口语，常作 largarse）离开&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1662" s="1" t="inlineStr">
@@ -53509,7 +53597,7 @@
       </c>
       <c r="D1662" s="1" t="inlineStr">
         <is>
-          <t>离开</t>
+          <t>松开；放出；（口语，常作 largarse）离开&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1662" s="1" t="inlineStr">
@@ -54085,7 +54173,7 @@
       </c>
       <c r="D1680" s="1" t="inlineStr">
         <is>
-          <t>收到</t>
+          <t>拼写错误，应为 recibir：收到&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1680" s="1" t="inlineStr">
@@ -54427,7 +54515,7 @@
       </c>
       <c r="B1691" s="1" t="inlineStr">
         <is>
-          <t>[fiɾˈmaɾ] 标志&lt;动&gt;</t>
+          <t>[/fiɾˈmaɾ/] 签名；签署&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1691" s="1" t="inlineStr">
@@ -54437,7 +54525,7 @@
       </c>
       <c r="D1691" s="1" t="inlineStr">
         <is>
-          <t>标志</t>
+          <t>签名；签署</t>
         </is>
       </c>
       <c r="E1691" s="1" t="inlineStr">
@@ -54811,7 +54899,7 @@
       </c>
       <c r="B1703" s="1" t="inlineStr">
         <is>
-          <t>[peɾsoˈnaxe] 性格&lt;名&gt;</t>
+          <t>[/peɾsoˈnaxe/] 人物；角色&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1703" s="1" t="inlineStr">
@@ -54821,7 +54909,7 @@
       </c>
       <c r="D1703" s="1" t="inlineStr">
         <is>
-          <t>性格</t>
+          <t>人物；角色</t>
         </is>
       </c>
       <c r="E1703" s="1" t="inlineStr">
@@ -55259,7 +55347,7 @@
       </c>
       <c r="B1717" s="1" t="inlineStr">
         <is>
-          <t>[ˈθjeɡo] 盲人&lt;名&gt;</t>
+          <t>[/ˈθjeɡo/] 盲的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1717" s="1" t="inlineStr">
@@ -55269,7 +55357,7 @@
       </c>
       <c r="D1717" s="1" t="inlineStr">
         <is>
-          <t>盲人</t>
+          <t>盲的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1717" s="1" t="inlineStr">
@@ -55291,7 +55379,7 @@
       </c>
       <c r="B1718" s="1" t="inlineStr">
         <is>
-          <t>[ˈxo] 乔&lt;叹&gt;</t>
+          <t>[/ˈxo/] 哎；啧（表示恼怒的感叹词）&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C1718" s="1" t="inlineStr">
@@ -55301,7 +55389,7 @@
       </c>
       <c r="D1718" s="1" t="inlineStr">
         <is>
-          <t>乔</t>
+          <t>哎；啧（表示恼怒的感叹词）</t>
         </is>
       </c>
       <c r="E1718" s="1" t="inlineStr">
@@ -56347,7 +56435,7 @@
       </c>
       <c r="B1751" s="1" t="inlineStr">
         <is>
-          <t>[ˈumo] 抽烟&lt;名&gt;</t>
+          <t>[/ˈumo/] 烟；烟雾&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1751" s="1" t="inlineStr">
@@ -56357,7 +56445,7 @@
       </c>
       <c r="D1751" s="1" t="inlineStr">
         <is>
-          <t>抽烟</t>
+          <t>烟；烟雾</t>
         </is>
       </c>
       <c r="E1751" s="1" t="inlineStr">
@@ -56507,7 +56595,7 @@
       </c>
       <c r="B1756" s="1" t="inlineStr">
         <is>
-          <t>[saˈlaɾ] 盐&lt;名&gt;</t>
+          <t>[/saˈlaɾ/] 加盐；腌制&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1756" s="1" t="inlineStr">
@@ -56517,7 +56605,7 @@
       </c>
       <c r="D1756" s="1" t="inlineStr">
         <is>
-          <t>盐</t>
+          <t>加盐；腌制</t>
         </is>
       </c>
       <c r="E1756" s="1" t="inlineStr">
@@ -56670,7 +56758,11 @@
           <t>这个&lt;代&gt;</t>
         </is>
       </c>
-      <c r="C1761" s="1" t="inlineStr"/>
+      <c r="C1761" s="1" t="inlineStr">
+        <is>
+          <t>/ˈesto/</t>
+        </is>
+      </c>
       <c r="D1761" s="1" t="inlineStr">
         <is>
           <t>这个</t>
@@ -56983,7 +57075,7 @@
       </c>
       <c r="B1771" s="1" t="inlineStr">
         <is>
-          <t>[ˈmis] 想念&lt;名&gt;</t>
+          <t>[/ˈmis/] 小姐；姑娘&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1771" s="1" t="inlineStr">
@@ -56993,7 +57085,7 @@
       </c>
       <c r="D1771" s="1" t="inlineStr">
         <is>
-          <t>想念</t>
+          <t>小姐；姑娘</t>
         </is>
       </c>
       <c r="E1771" s="1" t="inlineStr">
@@ -57527,7 +57619,7 @@
       </c>
       <c r="B1788" s="1" t="inlineStr">
         <is>
-          <t>[ˈabɾa] 打开&lt;名&gt;</t>
+          <t>[/ˈabɾa/] 小海湾；山口&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1788" s="1" t="inlineStr">
@@ -57537,7 +57629,7 @@
       </c>
       <c r="D1788" s="1" t="inlineStr">
         <is>
-          <t>打开</t>
+          <t>小海湾；山口</t>
         </is>
       </c>
       <c r="E1788" s="1" t="inlineStr">
@@ -57591,7 +57683,7 @@
       </c>
       <c r="B1790" s="1" t="inlineStr">
         <is>
-          <t>[ˈkonde] 计数&lt;名&gt;</t>
+          <t>[/ˈkonde/] 伯爵&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1790" s="1" t="inlineStr">
@@ -57601,7 +57693,7 @@
       </c>
       <c r="D1790" s="1" t="inlineStr">
         <is>
-          <t>计数</t>
+          <t>伯爵</t>
         </is>
       </c>
       <c r="E1790" s="1" t="inlineStr">
@@ -57815,7 +57907,7 @@
       </c>
       <c r="B1797" s="1" t="inlineStr">
         <is>
-          <t>[ˈθjaɾ] 西亚尔&lt;动&gt;</t>
+          <t>[/ˈθjaɾ/] 搅拌；搅动&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1797" s="1" t="inlineStr">
@@ -57825,7 +57917,7 @@
       </c>
       <c r="D1797" s="1" t="inlineStr">
         <is>
-          <t>西亚尔</t>
+          <t>搅拌；搅动</t>
         </is>
       </c>
       <c r="E1797" s="1" t="inlineStr">
@@ -57911,7 +58003,7 @@
       </c>
       <c r="B1800" s="1" t="inlineStr">
         <is>
-          <t>[ˈluka] 卢克&lt;名&gt;</t>
+          <t>[/ˈluka/] 千元钞票；一千（比索，口语）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1800" s="1" t="inlineStr">
@@ -57921,7 +58013,7 @@
       </c>
       <c r="D1800" s="1" t="inlineStr">
         <is>
-          <t>卢克</t>
+          <t>千元钞票；一千（比索，口语）</t>
         </is>
       </c>
       <c r="E1800" s="1" t="inlineStr">
@@ -58007,7 +58099,7 @@
       </c>
       <c r="B1803" s="1" t="inlineStr">
         <is>
-          <t>[ˈteto] 山雀&lt;名&gt;</t>
+          <t>[/ˈteto/] 屋顶（口语）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1803" s="1" t="inlineStr">
@@ -58017,7 +58109,7 @@
       </c>
       <c r="D1803" s="1" t="inlineStr">
         <is>
-          <t>山雀</t>
+          <t>屋顶（口语）</t>
         </is>
       </c>
       <c r="E1803" s="1" t="inlineStr">
@@ -58135,7 +58227,7 @@
       </c>
       <c r="B1807" s="1" t="inlineStr">
         <is>
-          <t>[ˈbolo] 丸剂&lt;名&gt;</t>
+          <t>[/ˈbolo/] 保龄球；木瓶（也指一剂毒品）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1807" s="1" t="inlineStr">
@@ -58145,7 +58237,7 @@
       </c>
       <c r="D1807" s="1" t="inlineStr">
         <is>
-          <t>丸剂</t>
+          <t>保龄球；木瓶（也指一剂毒品）</t>
         </is>
       </c>
       <c r="E1807" s="1" t="inlineStr">
@@ -58423,7 +58515,7 @@
       </c>
       <c r="B1816" s="1" t="inlineStr">
         <is>
-          <t>[ˈroka] 摇滚&lt;名&gt;</t>
+          <t>[/ˈroka/] 岩石&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1816" s="1" t="inlineStr">
@@ -58433,7 +58525,7 @@
       </c>
       <c r="D1816" s="1" t="inlineStr">
         <is>
-          <t>摇滚</t>
+          <t>岩石</t>
         </is>
       </c>
       <c r="E1816" s="1" t="inlineStr">
@@ -58682,7 +58774,11 @@
           <t>女士&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1824" s="1" t="inlineStr"/>
+      <c r="C1824" s="1" t="inlineStr">
+        <is>
+          <t>/madˈame/</t>
+        </is>
+      </c>
       <c r="D1824" s="1" t="inlineStr">
         <is>
           <t>女士</t>
@@ -58739,7 +58835,7 @@
       </c>
       <c r="B1826" s="1" t="inlineStr">
         <is>
-          <t>[diɾiˈxiɾ] 铅&lt;动&gt;</t>
+          <t>[/diɾiˈxiɾ/] 领导；指导；管理&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1826" s="1" t="inlineStr">
@@ -58749,7 +58845,7 @@
       </c>
       <c r="D1826" s="1" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>领导；指导；管理</t>
         </is>
       </c>
       <c r="E1826" s="1" t="inlineStr">
@@ -58963,7 +59059,7 @@
       </c>
       <c r="B1833" s="1" t="inlineStr">
         <is>
-          <t>[ˈbeɡa] 织女星&lt;名&gt;</t>
+          <t>[/ˈbeɡa/] 河畔草地；沃土平原&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1833" s="1" t="inlineStr">
@@ -58973,7 +59069,7 @@
       </c>
       <c r="D1833" s="1" t="inlineStr">
         <is>
-          <t>织女星</t>
+          <t>河畔草地；沃土平原</t>
         </is>
       </c>
       <c r="E1833" s="1" t="inlineStr">
@@ -58995,7 +59091,7 @@
       </c>
       <c r="B1834" s="1" t="inlineStr">
         <is>
-          <t>[ˈpaɾe] 停止&lt;名&gt;</t>
+          <t>[/ˈpaɾe/] 停止&lt;动&gt;（parar 的动词变位形式）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1834" s="1" t="inlineStr">
@@ -59005,7 +59101,7 @@
       </c>
       <c r="D1834" s="1" t="inlineStr">
         <is>
-          <t>停止</t>
+          <t>停止&lt;动&gt;（parar 的动词变位形式）</t>
         </is>
       </c>
       <c r="E1834" s="1" t="inlineStr">
@@ -59155,7 +59251,7 @@
       </c>
       <c r="B1839" s="1" t="inlineStr">
         <is>
-          <t>[paˈtɾon] 图案&lt;名&gt;</t>
+          <t>[/paˈtɾon/] 老板，雇主；模式&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1839" s="1" t="inlineStr">
@@ -59165,7 +59261,7 @@
       </c>
       <c r="D1839" s="1" t="inlineStr">
         <is>
-          <t>图案</t>
+          <t>老板，雇主；模式</t>
         </is>
       </c>
       <c r="E1839" s="1" t="inlineStr">
@@ -59379,7 +59475,7 @@
       </c>
       <c r="B1846" s="1" t="inlineStr">
         <is>
-          <t>[meˈdida] 测量&lt;名&gt;</t>
+          <t>[/meˈdida/] 措施；尺寸&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1846" s="1" t="inlineStr">
@@ -59389,7 +59485,7 @@
       </c>
       <c r="D1846" s="1" t="inlineStr">
         <is>
-          <t>测量</t>
+          <t>措施；尺寸</t>
         </is>
       </c>
       <c r="E1846" s="1" t="inlineStr">
@@ -59603,7 +59699,7 @@
       </c>
       <c r="B1853" s="1" t="inlineStr">
         <is>
-          <t>[ˈma] 马&lt;名&gt;</t>
+          <t>[/ˈma/] 妈；妈妈&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1853" s="1" t="inlineStr">
@@ -59613,7 +59709,7 @@
       </c>
       <c r="D1853" s="1" t="inlineStr">
         <is>
-          <t>马</t>
+          <t>妈；妈妈</t>
         </is>
       </c>
       <c r="E1853" s="1" t="inlineStr">
@@ -59731,7 +59827,7 @@
       </c>
       <c r="B1857" s="1" t="inlineStr">
         <is>
-          <t>[ˈmina] 我的&lt;名&gt;</t>
+          <t>[/ˈmina/] 矿山；矿井；地雷&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1857" s="1" t="inlineStr">
@@ -59741,7 +59837,7 @@
       </c>
       <c r="D1857" s="1" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>矿山；矿井；地雷</t>
         </is>
       </c>
       <c r="E1857" s="1" t="inlineStr">
@@ -59859,7 +59955,7 @@
       </c>
       <c r="B1861" s="1" t="inlineStr">
         <is>
-          <t>[koθiˈnaɾ] 厨师&lt;动&gt;</t>
+          <t>[/koθiˈnaɾ/] 烹调；烹饪；做饭&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1861" s="1" t="inlineStr">
@@ -59869,7 +59965,7 @@
       </c>
       <c r="D1861" s="1" t="inlineStr">
         <is>
-          <t>厨师</t>
+          <t>烹调；烹饪；做饭</t>
         </is>
       </c>
       <c r="E1861" s="1" t="inlineStr">
@@ -60083,7 +60179,7 @@
       </c>
       <c r="B1868" s="1" t="inlineStr">
         <is>
-          <t>[maɾaˈbiʝa] 想知道&lt;名&gt;</t>
+          <t>[/maɾaˈbiʝa/] 奇迹；奇观；奇妙的事物&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1868" s="1" t="inlineStr">
@@ -60093,7 +60189,7 @@
       </c>
       <c r="D1868" s="1" t="inlineStr">
         <is>
-          <t>想知道</t>
+          <t>奇迹；奇观；奇妙的事物</t>
         </is>
       </c>
       <c r="E1868" s="1" t="inlineStr">
@@ -60115,7 +60211,7 @@
       </c>
       <c r="B1869" s="1" t="inlineStr">
         <is>
-          <t>[ˈkita] 删除&lt;名&gt;</t>
+          <t>[/ˈkita/] 减免；免除&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1869" s="1" t="inlineStr">
@@ -60125,7 +60221,7 @@
       </c>
       <c r="D1869" s="1" t="inlineStr">
         <is>
-          <t>删除</t>
+          <t>减免；免除&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1869" s="1" t="inlineStr">
@@ -60211,7 +60307,7 @@
       </c>
       <c r="B1872" s="1" t="inlineStr">
         <is>
-          <t>[ˈbombo] 炒作&lt;名&gt;</t>
+          <t>[/ˈbombo/] 大鼓；鼓；宣传&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1872" s="1" t="inlineStr">
@@ -60221,7 +60317,7 @@
       </c>
       <c r="D1872" s="1" t="inlineStr">
         <is>
-          <t>炒作</t>
+          <t>大鼓；鼓；宣传</t>
         </is>
       </c>
       <c r="E1872" s="1" t="inlineStr">
@@ -60438,7 +60534,11 @@
           <t>[seˈɣundo] 秒；秒钟&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1879" s="1" t="inlineStr"/>
+      <c r="C1879" s="1" t="inlineStr">
+        <is>
+          <t>/seˈɣundo/</t>
+        </is>
+      </c>
       <c r="D1879" s="1" t="inlineStr">
         <is>
           <t>秒</t>
@@ -60559,7 +60659,7 @@
       </c>
       <c r="B1883" s="1" t="inlineStr">
         <is>
-          <t>[kɾuˈθaɾ] 十字&lt;动&gt;</t>
+          <t>[/kɾuˈθaɾ/] 穿过；横穿；交叉&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1883" s="1" t="inlineStr">
@@ -60569,7 +60669,7 @@
       </c>
       <c r="D1883" s="1" t="inlineStr">
         <is>
-          <t>十字</t>
+          <t>穿过；横穿；交叉</t>
         </is>
       </c>
       <c r="E1883" s="1" t="inlineStr">
@@ -60658,7 +60758,11 @@
           <t>我看&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1886" s="1" t="inlineStr"/>
+      <c r="C1886" s="1" t="inlineStr">
+        <is>
+          <t>/ˈmiɾo/</t>
+        </is>
+      </c>
       <c r="D1886" s="1" t="inlineStr">
         <is>
           <t>我看</t>
@@ -62187,7 +62291,7 @@
       </c>
       <c r="B1934" s="1" t="inlineStr">
         <is>
-          <t>[θeɾˈkano] 关闭&lt;形&gt;</t>
+          <t>[/θeɾˈkano/] 近的；附近的；接近的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1934" s="1" t="inlineStr">
@@ -62197,7 +62301,7 @@
       </c>
       <c r="D1934" s="1" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>近的；附近的；接近的</t>
         </is>
       </c>
       <c r="E1934" s="1" t="inlineStr">
@@ -62539,7 +62643,7 @@
       </c>
       <c r="B1945" s="1" t="inlineStr">
         <is>
-          <t>[ˈronda] 圆形&lt;名&gt;</t>
+          <t>[/ˈronda/] 巡逻；环线；轮次&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1945" s="1" t="inlineStr">
@@ -62549,7 +62653,7 @@
       </c>
       <c r="D1945" s="1" t="inlineStr">
         <is>
-          <t>圆形</t>
+          <t>巡逻；环线；轮次</t>
         </is>
       </c>
       <c r="E1945" s="1" t="inlineStr">
@@ -62987,7 +63091,7 @@
       </c>
       <c r="B1959" s="1" t="inlineStr">
         <is>
-          <t>[komeˈtido] 致力于&lt;名&gt;</t>
+          <t>[/komeˈtido/] 任务；职责；使命&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1959" s="1" t="inlineStr">
@@ -62997,7 +63101,7 @@
       </c>
       <c r="D1959" s="1" t="inlineStr">
         <is>
-          <t>致力于</t>
+          <t>任务；职责；使命</t>
         </is>
       </c>
       <c r="E1959" s="1" t="inlineStr">
@@ -63179,7 +63283,7 @@
       </c>
       <c r="B1965" s="1" t="inlineStr">
         <is>
-          <t>[ˈbota] 启动&lt;名&gt;</t>
+          <t>[/ˈbota/] 靴子&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1965" s="1" t="inlineStr">
@@ -63189,7 +63293,7 @@
       </c>
       <c r="D1965" s="1" t="inlineStr">
         <is>
-          <t>启动</t>
+          <t>靴子</t>
         </is>
       </c>
       <c r="E1965" s="1" t="inlineStr">
@@ -63659,7 +63763,7 @@
       </c>
       <c r="B1980" s="1" t="inlineStr">
         <is>
-          <t>[ˈkwadɾo] 盒子&lt;名&gt;</t>
+          <t>[/ˈkwadɾo/] 图画；绘画；方格；框架&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1980" s="1" t="inlineStr">
@@ -63669,7 +63773,7 @@
       </c>
       <c r="D1980" s="1" t="inlineStr">
         <is>
-          <t>盒子</t>
+          <t>图画；绘画；方格；框架</t>
         </is>
       </c>
       <c r="E1980" s="1" t="inlineStr">
@@ -63726,7 +63830,11 @@
           <t>日本&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1982" s="1" t="inlineStr"/>
+      <c r="C1982" s="1" t="inlineStr">
+        <is>
+          <t>/xaˈpon/</t>
+        </is>
+      </c>
       <c r="D1982" s="1" t="inlineStr">
         <is>
           <t>日本</t>
